--- a/Lazarus/RecorderLnx/Docs/devices/mic140/Расчет точек АЦП.xlsx
+++ b/Lazarus/RecorderLnx/Docs/devices/mic140/Расчет точек АЦП.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\works\OburecGH\Lazarus\RecorderLnx\Docs\devices\mic140\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C551587A-B7C2-4D76-81CC-CAF959E87FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C963B7-E936-484A-8EC2-CD40565F2C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{259C84DC-4674-48B3-A586-46148F7BB952}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>fs</t>
   </si>
@@ -109,6 +109,9 @@
   </si>
   <si>
     <t>Старт АЦП → RegLatch, uS</t>
+  </si>
+  <si>
+    <t>7 - температурных v3 mic140</t>
   </si>
 </sst>
 </file>
@@ -134,7 +137,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -159,6 +162,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -172,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -200,6 +209,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -344,6 +356,50 @@
         <a:xfrm>
           <a:off x="3705225" y="6534150"/>
           <a:ext cx="2648320" cy="409632"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>75384</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>9369</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Рисунок 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32B945EC-61C5-D803-F798-BCBD005FDB3F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6115050" y="3467100"/>
+          <a:ext cx="6523809" cy="1247619"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -701,7 +757,7 @@
         <v>0.1</v>
       </c>
       <c r="D7" s="6">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E7" s="10">
         <f>D37/1000</f>
@@ -709,13 +765,13 @@
       </c>
       <c r="F7" s="10">
         <f>E7/D7*10^6</f>
-        <v>1668.752607425949</v>
+        <v>1547.3887814313346</v>
       </c>
       <c r="G7" s="7">
         <v>0.84399999999999997</v>
       </c>
       <c r="H7" s="6">
-        <v>500</v>
+        <v>57</v>
       </c>
       <c r="I7" s="6">
         <v>19.687999999999999</v>
@@ -725,7 +781,7 @@
       </c>
       <c r="K7" s="7">
         <f>(F7-H7-I7-G7)/J7</f>
-        <v>229.64412148518977</v>
+        <v>293.97135628626688</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.25">
@@ -740,9 +796,12 @@
       <c r="G12" s="1">
         <v>2</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="11" t="s">
         <v>15</v>
       </c>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
     </row>
     <row r="13" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F13" s="2" t="s">
@@ -767,7 +826,7 @@
       <c r="F15" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="12">
         <f>G13/(2*G14)</f>
         <v>20</v>
       </c>
@@ -842,6 +901,9 @@
       </c>
       <c r="E25" s="4">
         <v>10000</v>
+      </c>
+      <c r="I25" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
@@ -956,8 +1018,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="B32:F32"/>
+    <mergeCell ref="H12:K12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
